--- a/산출물/대전3반_7팀__AIOnBoard_실습기획서.xlsx
+++ b/산출물/대전3반_7팀__AIOnBoard_실습기획서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SSAFY\WORKSPACE\1. Startcamp\vibecoding_teampjt\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8755000-B4E3-420D-9211-88D0D1B78B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DEA986-6E0B-4C86-BEDC-8237F5BA0BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16365" yWindow="4515" windowWidth="21375" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16710" yWindow="4860" windowWidth="21375" windowHeight="15345" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0_사용안내" sheetId="1" r:id="rId1"/>
@@ -3997,27 +3997,6 @@
     <t>챗봇 API(POST /api/chat) 기본 골격, 대화 히스토리 저장 구조, 공공데이터 JSON 파싱·적재</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>최지욱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>(BE)</t>
-    </r>
-  </si>
-  <si>
     <t>게시판 CRUD API ↔ FE 화면 연동, 비밀번호 기반 수정/삭제 권한 처리, 지도 컴포넌트에 게시글 마커 연동</t>
   </si>
   <si>
@@ -4054,36 +4033,6 @@
     <t>챗봇 API ↔ 채팅 UI 연동, 사투리 응답 프롬프트 튜닝, 관광지 룰렛 UI-데이터 연동</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>박유빈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>최지욱</t>
-    </r>
-  </si>
-  <si>
     <t>테스트</t>
   </si>
   <si>
@@ -4094,36 +4043,6 @@
   </si>
   <si>
     <t>Render BE 배포, 환경변수 설정, API 도메인 확정</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>신규철</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>최지욱</t>
-    </r>
   </si>
   <si>
     <t>진행중</t>
@@ -5581,6 +5500,95 @@
         <family val="2"/>
       </rPr>
       <t>)</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최진욱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(BE)</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>박유빈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최진욱</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신규철</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최진욱</t>
     </r>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
@@ -6046,43 +6054,6 @@
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6168,31 +6139,65 @@
     <xf numFmtId="176" fontId="36" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6210,17 +6215,20 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6511,120 +6519,120 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="31.5" customHeight="1">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="36.75" customHeight="1">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12"/>
+      <c r="C9" s="33"/>
     </row>
     <row r="10" spans="2:3" ht="27" customHeight="1">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="40.5" customHeight="1">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="33.75" customHeight="1">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="34"/>
     </row>
     <row r="18" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="35"/>
     </row>
     <row r="19" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="9"/>
+      <c r="C19" s="31"/>
     </row>
     <row r="20" spans="2:3" ht="27.75" customHeight="1">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="31"/>
     </row>
     <row r="21" spans="2:3" ht="27.75" customHeight="1"/>
   </sheetData>
@@ -6658,144 +6666,144 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="30" customHeight="1">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="4" spans="2:10" ht="19.5" customHeight="1">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="129.75" customHeight="1">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="129.75" customHeight="1">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="129.75" customHeight="1">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="129.75" customHeight="1">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="13.5" customHeight="1"/>
     <row r="10" spans="2:10" ht="15" customHeight="1">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
     </row>
     <row r="11" spans="2:10" ht="24" customHeight="1">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
     </row>
     <row r="12" spans="2:10" ht="24" customHeight="1">
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
     </row>
     <row r="13" spans="2:10" ht="24" customHeight="1">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6820,280 +6828,280 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="10" style="60" customWidth="1"/>
+    <col min="2" max="2" width="10" style="30" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="57.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="60" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="30" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
     </row>
     <row r="4" spans="2:6" ht="35.25" customHeight="1">
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="25.5">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="27">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="C6" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="25.5">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="38.25">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="40.5">
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="C9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="38.25">
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="6" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="38.25">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="25.5">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="38.25">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="6" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="38.25">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="30" customHeight="1">
-      <c r="B15" s="36"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="2:6" ht="30" customHeight="1">
-      <c r="B16" s="36"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="2:6" ht="30" customHeight="1">
-      <c r="B17" s="36"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="19"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="2:6" ht="30" customHeight="1">
-      <c r="B18" s="36"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="19"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="2:6" ht="30" customHeight="1">
-      <c r="B19" s="36"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="19"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="2:6" ht="30" customHeight="1">
-      <c r="B20" s="36"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
-      <c r="B21" s="36"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="19"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="2:6" ht="30" customHeight="1">
-      <c r="B22" s="36"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="19"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="2:6" ht="30" customHeight="1">
-      <c r="B23" s="36"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="19"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7129,253 +7137,253 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="2:8" ht="72" customHeight="1">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="2:8" ht="18" customHeight="1">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="2:8" ht="31.5" customHeight="1">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="H5" s="21" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="13">
         <v>5</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="13">
         <v>5</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="23">
         <f t="shared" ref="G6:G13" si="0">IF(OR(E6="",F6=""),"",E6*F6*2)</f>
         <v>50</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="13">
         <v>2</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="13">
         <v>5</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="13">
         <v>4</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="23">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="13">
         <v>2</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="13">
         <v>5</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="13">
         <v>4</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="23">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="13">
         <v>3</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="13">
         <v>4</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="13">
         <v>4</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="23">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="24" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="13">
         <v>4</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="13">
         <v>2</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="13">
         <v>3</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="24" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="13">
         <v>2</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="13">
         <v>3</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="13">
         <v>2</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="24" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="13">
         <v>3</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="13">
         <v>3</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="13">
         <v>3</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="23">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="24" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1">
-      <c r="B13" s="35"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="36" t="str">
+      <c r="B13" s="22"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="H13" s="37"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="15" spans="2:8" ht="118.5" customHeight="1">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
+      <c r="C15" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7420,108 +7428,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="39"/>
     </row>
     <row r="3" spans="2:3" ht="18" customHeight="1">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="48"/>
     </row>
     <row r="4" spans="2:3" ht="30" customHeight="1">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="30" customHeight="1">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="30" customHeight="1">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="6" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="30" customHeight="1">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="43"/>
+      <c r="C9" s="49"/>
     </row>
     <row r="10" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="45"/>
     </row>
     <row r="11" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="C11" s="44"/>
+      <c r="C11" s="45"/>
     </row>
     <row r="12" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="35"/>
     </row>
     <row r="13" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="35"/>
     </row>
     <row r="14" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="44"/>
+      <c r="C14" s="45"/>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="C16" s="45"/>
+      <c r="C16" s="47"/>
     </row>
     <row r="17" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="45"/>
     </row>
     <row r="18" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="44"/>
+      <c r="C18" s="45"/>
     </row>
     <row r="19" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="C19" s="44"/>
+      <c r="C19" s="45"/>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
       <c r="B21" s="46" t="s">
@@ -7530,41 +7538,41 @@
       <c r="C21" s="46"/>
     </row>
     <row r="22" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="45"/>
     </row>
     <row r="23" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="44"/>
+      <c r="C23" s="45"/>
     </row>
     <row r="24" spans="2:3" ht="25.5" customHeight="1">
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="44"/>
+      <c r="C24" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7594,604 +7602,604 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="27.75" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
     </row>
     <row r="3" spans="2:13" ht="79.5" customHeight="1">
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="2:13" ht="25.5" customHeight="1">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="27" t="s">
         <v>166</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="K4" s="42">
+      <c r="K4" s="29">
         <v>1</v>
       </c>
-      <c r="L4" s="42">
+      <c r="L4" s="29">
         <v>2</v>
       </c>
-      <c r="M4" s="42">
+      <c r="M4" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="51">
-      <c r="B5" s="26">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="13">
         <v>1</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="13">
         <v>1</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="13">
         <f t="shared" ref="H5:H18" si="0">IF(OR(F5="",G5=""),"",G5-F5+1)</f>
         <v>1</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="13">
         <v>100</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="2:13" ht="25.5">
-      <c r="B6" s="26">
+      <c r="B6" s="13">
         <v>2</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="13">
         <v>1</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="13">
         <v>100</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="2:13" ht="38.25">
-      <c r="B7" s="26">
+      <c r="B7" s="13">
         <v>3</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="13">
         <v>1</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="13">
         <v>1</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="13">
         <v>100</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" spans="2:13" ht="38.25">
-      <c r="B8" s="26">
+      <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="13">
         <v>1</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="13">
         <v>1</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="13">
         <v>100</v>
       </c>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" spans="2:13" ht="51">
-      <c r="B9" s="26">
+      <c r="B9" s="13">
         <v>5</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="13">
         <v>1</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="13">
         <v>1</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="13">
         <v>100</v>
       </c>
-      <c r="J9" s="37" t="s">
+      <c r="J9" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="2:13" ht="51">
-      <c r="B10" s="26">
+      <c r="B10" s="13">
         <v>6</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="26">
+      <c r="E10" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="F10" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="13">
         <v>1</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="13">
         <v>100</v>
       </c>
-      <c r="J10" s="37" t="s">
+      <c r="J10" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" spans="2:13" ht="63.75">
-      <c r="B11" s="26">
+      <c r="B11" s="13">
         <v>7</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="26">
+      <c r="F11" s="13">
         <v>2</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="13">
         <v>2</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="13">
         <v>100</v>
       </c>
-      <c r="J11" s="37" t="s">
+      <c r="J11" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" spans="2:13" ht="51">
-      <c r="B12" s="26">
+      <c r="B12" s="13">
         <v>8</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="26">
+      <c r="D12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="13">
         <v>2</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="13">
         <v>2</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="13">
         <v>100</v>
       </c>
-      <c r="J12" s="37" t="s">
+      <c r="J12" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" spans="2:13" ht="30" customHeight="1">
-      <c r="B13" s="26">
+      <c r="B13" s="13">
         <v>9</v>
       </c>
-      <c r="C13" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E13" s="37" t="s">
+      <c r="C13" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="13">
         <v>2</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="13">
         <v>2</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="13">
         <v>100</v>
       </c>
-      <c r="J13" s="37" t="s">
+      <c r="J13" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-    </row>
-    <row r="14" spans="2:13" ht="25.5">
-      <c r="B14" s="26">
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="2:13" ht="27">
+      <c r="B14" s="13">
         <v>10</v>
       </c>
-      <c r="C14" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="F14" s="26">
+      <c r="C14" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" s="13">
         <v>3</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="13">
         <v>3</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="13">
         <v>80</v>
       </c>
-      <c r="J14" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
+      <c r="J14" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:13" ht="38.25">
-      <c r="B15" s="26">
+      <c r="B15" s="13">
         <v>11</v>
       </c>
-      <c r="C15" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="F15" s="26">
+      <c r="C15" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="13">
         <v>3</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="13">
         <v>3</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="13">
         <v>70</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="2:13" ht="30" customHeight="1">
+      <c r="B16" s="13">
+        <v>12</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-    </row>
-    <row r="16" spans="2:13" ht="30" customHeight="1">
-      <c r="B16" s="26">
-        <v>12</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="13">
         <v>3</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="13">
         <v>3</v>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="13">
         <v>50</v>
       </c>
-      <c r="J16" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
+      <c r="J16" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" spans="2:13" ht="30" customHeight="1">
-      <c r="B17" s="26">
+      <c r="B17" s="13">
         <v>13</v>
       </c>
-      <c r="C17" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="E17" s="37" t="s">
+      <c r="C17" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="13">
         <v>3</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="13">
         <v>3</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="13">
         <v>40</v>
       </c>
-      <c r="J17" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
+      <c r="J17" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" spans="2:13" ht="30" customHeight="1">
-      <c r="B18" s="26">
+      <c r="B18" s="13">
         <v>14</v>
       </c>
-      <c r="C18" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" s="37" t="s">
+      <c r="C18" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="13">
         <v>3</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="13">
         <v>3</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="13">
         <v>0</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="J18" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1">
-      <c r="B20" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="49"/>
+      <c r="B20" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="58"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1">
-      <c r="B21" s="50" t="s">
+      <c r="B21" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="50"/>
+      <c r="C21" s="59"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="51"/>
+      <c r="C22" s="60"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1">
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="C23" s="52"/>
+      <c r="C23" s="51"/>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1">
-      <c r="B24" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="53"/>
+      <c r="B24" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="52"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1">
-      <c r="B25" s="54" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="54"/>
+      <c r="B25" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" s="53"/>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1">
-      <c r="B26" s="55" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="55"/>
+      <c r="B26" s="54" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="54"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1">
-      <c r="B27" s="56" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="56"/>
+      <c r="B27" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="55"/>
     </row>
     <row r="28" spans="2:13" ht="15" customHeight="1">
-      <c r="B28" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="C28" s="57"/>
+      <c r="B28" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="K5:M18">
@@ -8228,183 +8236,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="36"/>
+    </row>
+    <row r="3" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B3" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="42"/>
+    </row>
+    <row r="5" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B5" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="6" spans="2:3" ht="30" customHeight="1">
+      <c r="B6" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="5" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B5" s="20" t="s">
+      <c r="C6" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C5" s="20" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="30" customHeight="1">
+      <c r="B7" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="30" customHeight="1">
-      <c r="B6" s="18" t="s">
+      <c r="C7" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="19" t="s">
+    </row>
+    <row r="8" spans="2:3" ht="30" customHeight="1">
+      <c r="B8" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="30" customHeight="1">
-      <c r="B7" s="18" t="s">
+      <c r="C8" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="19" t="s">
+    </row>
+    <row r="9" spans="2:3" ht="30" customHeight="1">
+      <c r="B9" s="3" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="30" customHeight="1">
-      <c r="B8" s="18" t="s">
+      <c r="C9" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="19" t="s">
+    </row>
+    <row r="10" spans="2:3" ht="30" customHeight="1">
+      <c r="B10" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" ht="30" customHeight="1">
-      <c r="B9" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C9" s="19" t="s">
+    </row>
+    <row r="11" spans="2:3" ht="30" customHeight="1">
+      <c r="B11" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" ht="30" customHeight="1">
-      <c r="B10" s="18" t="s">
+      <c r="C11" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="19" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="30" customHeight="1">
+      <c r="B12" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="30" customHeight="1">
-      <c r="B11" s="18" t="s">
+      <c r="C12" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C11" s="19" t="s">
+    </row>
+    <row r="13" spans="2:3" ht="30" customHeight="1">
+      <c r="B13" s="3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" ht="30" customHeight="1">
-      <c r="B12" s="18" t="s">
+      <c r="C13" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="C12" s="19" t="s">
+    </row>
+    <row r="14" spans="2:3" ht="30" customHeight="1">
+      <c r="B14" s="5" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" ht="30" customHeight="1">
-      <c r="B13" s="16" t="s">
+      <c r="C14" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="19" t="s">
+    </row>
+    <row r="15" spans="2:3" ht="30" customHeight="1">
+      <c r="B15" s="3" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" ht="30" customHeight="1">
-      <c r="B14" s="18" t="s">
+      <c r="C15" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C14" s="19" t="s">
+    </row>
+    <row r="16" spans="2:3" ht="30" customHeight="1">
+      <c r="B16" s="3" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" ht="30" customHeight="1">
-      <c r="B15" s="16" t="s">
+      <c r="C16" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="19" t="s">
+    </row>
+    <row r="17" spans="2:3" ht="30" customHeight="1">
+      <c r="B17" s="5" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" ht="30" customHeight="1">
-      <c r="B16" s="16" t="s">
+      <c r="C17" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C16" s="19" t="s">
+    </row>
+    <row r="18" spans="2:3" ht="30" customHeight="1">
+      <c r="B18" s="3" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1">
-      <c r="B17" s="18" t="s">
+      <c r="C18" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="C17" s="19" t="s">
+    </row>
+    <row r="19" spans="2:3" ht="30" customHeight="1">
+      <c r="B19" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="30" customHeight="1">
-      <c r="B18" s="16" t="s">
+      <c r="C19" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="19" t="s">
+    </row>
+    <row r="20" spans="2:3" ht="30" customHeight="1">
+      <c r="B20" s="3" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" ht="30" customHeight="1">
-      <c r="B19" s="16" t="s">
+      <c r="C20" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C19" s="19" t="s">
+    </row>
+    <row r="21" spans="2:3" ht="30" customHeight="1">
+      <c r="B21" s="3" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" ht="30" customHeight="1">
-      <c r="B20" s="16" t="s">
+      <c r="C21" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C20" s="19" t="s">
+    </row>
+    <row r="22" spans="2:3" ht="30" customHeight="1">
+      <c r="B22" s="3" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="21" spans="2:3" ht="30" customHeight="1">
-      <c r="B21" s="16" t="s">
+      <c r="C22" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="C21" s="17" t="s">
+    </row>
+    <row r="23" spans="2:3" ht="30" customHeight="1">
+      <c r="B23" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" ht="30" customHeight="1">
-      <c r="B22" s="16" t="s">
+      <c r="C23" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="C22" s="19" t="s">
+    </row>
+    <row r="24" spans="2:3" ht="30" customHeight="1">
+      <c r="B24" s="5" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1">
-      <c r="B23" s="18" t="s">
+      <c r="C24" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="19" t="s">
+    </row>
+    <row r="25" spans="2:3" ht="30" customHeight="1">
+      <c r="B25" s="5" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1">
-      <c r="B24" s="18" t="s">
+      <c r="C25" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1">
-      <c r="B25" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -8414,6 +8422,6 @@
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>